--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.86628805455632</v>
+        <v>5.340771808865402</v>
       </c>
       <c r="D2" t="n">
-        <v>29.72438197371779</v>
+        <v>4.830212070729141</v>
       </c>
       <c r="E2" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F2" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.82989454215395</v>
+        <v>2.897357863100017</v>
       </c>
       <c r="D3" t="n">
-        <v>15.70732066046138</v>
+        <v>2.552439607324974</v>
       </c>
       <c r="E3" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F3" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.49747594266302</v>
+        <v>4.468339840682741</v>
       </c>
       <c r="D4" t="n">
-        <v>22.5331470136916</v>
+        <v>3.661636389724886</v>
       </c>
       <c r="E4" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F4" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.234374462736177</v>
+        <v>1.175585850194629</v>
       </c>
       <c r="D5" t="n">
-        <v>6.324555320336759</v>
+        <v>1.027740239554723</v>
       </c>
       <c r="E5" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F5" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.79351657246145</v>
+        <v>1.753946443024986</v>
       </c>
       <c r="D6" t="n">
-        <v>18.17481625297724</v>
+        <v>2.953407641108802</v>
       </c>
       <c r="E6" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F6" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.19378812591328</v>
+        <v>4.581490570460907</v>
       </c>
       <c r="D7" t="n">
-        <v>27.50454507895013</v>
+        <v>4.469488575329397</v>
       </c>
       <c r="E7" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F7" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.30639558435123</v>
+        <v>6.549789282457075</v>
       </c>
       <c r="D8" t="n">
-        <v>35.98731153236087</v>
+        <v>5.847938124008642</v>
       </c>
       <c r="E8" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F8" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.90801260963983</v>
+        <v>3.072552049066472</v>
       </c>
       <c r="D9" t="n">
-        <v>20.47786710421824</v>
+        <v>3.327653404435465</v>
       </c>
       <c r="E9" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F9" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.1624253165877</v>
+        <v>6.526394113945502</v>
       </c>
       <c r="D10" t="n">
-        <v>28.43093437438664</v>
+        <v>4.620026835837829</v>
       </c>
       <c r="E10" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F10" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.17948566318606</v>
+        <v>8.966666420267735</v>
       </c>
       <c r="D11" t="n">
-        <v>43.552041987468</v>
+        <v>7.07720682296355</v>
       </c>
       <c r="E11" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F11" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.05046038512227</v>
+        <v>4.39569981258237</v>
       </c>
       <c r="D12" t="n">
-        <v>15.84824883905006</v>
+        <v>2.575340436345634</v>
       </c>
       <c r="E12" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F12" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72227620396122</v>
+        <v>7.754869883143699</v>
       </c>
       <c r="D13" t="n">
-        <v>35.96691738705092</v>
+        <v>5.844624075395775</v>
       </c>
       <c r="E13" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F13" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.34173731167418</v>
+        <v>4.280532313147054</v>
       </c>
       <c r="D14" t="n">
-        <v>20.63748920393215</v>
+        <v>3.353591995638974</v>
       </c>
       <c r="E14" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F14" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>33.10810137517412</v>
+        <v>5.380066473465795</v>
       </c>
       <c r="D15" t="n">
-        <v>17.39012525187309</v>
+        <v>2.825895353429378</v>
       </c>
       <c r="E15" t="n">
-        <v>12.98918162458843</v>
+        <v>2.110742013995619</v>
       </c>
       <c r="F15" t="n">
-        <v>9.579112755108103</v>
+        <v>1.556605822705067</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
